--- a/check_mainspef_tretspef_inpatient_outpatient_ValidationStudy_GF.xlsx
+++ b/check_mainspef_tretspef_inpatient_outpatient_ValidationStudy_GF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms0952_ox_ac_uk/Documents/OMOP_Validation study/Secondary care analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{E031F84B-117C-48FB-A8A0-8BAE70C7D899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34937322-9531-4564-AF90-6CF81E5994E1}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{E031F84B-117C-48FB-A8A0-8BAE70C7D899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16A230CC-DB12-419D-B059-0A6E823F65F9}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{FC38C1A7-913E-488E-B731-6C19EF4AAE9E}"/>
   </bookViews>
@@ -498,7 +498,7 @@
     <t>haemophilia</t>
   </si>
   <si>
-    <t>Haemophilia Service</t>
+    <t>haemophilia service</t>
   </si>
   <si>
     <t>learning disability - specialty</t>
@@ -1009,7 +1009,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1154,6 +1154,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1497,7 +1503,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1509,6 +1515,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2005,6 +2012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B0CBA46-D5FA-4A1F-8AA3-0BA2E179936C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3363,16 +3371,16 @@
       <c r="B68" t="s">
         <v>151</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D68" s="3">
-        <v>318</v>
-      </c>
-      <c r="E68" s="2" t="s">
+      <c r="C68" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D68" s="5">
+        <v>303</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68" s="5">
         <v>309</v>
       </c>
     </row>
